--- a/Audit/JJ_PD_IP_D27_통합테스트계획서.xlsx
+++ b/Audit/JJ_PD_IP_D27_통합테스트계획서.xlsx
@@ -10634,7 +10634,7 @@
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
-          <t>- 안전위험35·민원25·이용20·사고20 가중치 종합점수 자동 산정, 요약·순위 정합</t>
+          <t>- 안전위험도·민원빈도·이용패턴·사고이력 가중치 종합점수 자동 산정, 요약·순위 정합</t>
         </is>
       </c>
       <c r="M30" s="67" t="inlineStr">

--- a/Audit/JJ_PD_IP_D27_통합테스트계획서.xlsx
+++ b/Audit/JJ_PD_IP_D27_통합테스트계획서.xlsx
@@ -9119,7 +9119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M61"/>
+  <dimension ref="A2:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5" customWidth="1" style="48" min="1" max="1"/>
@@ -10756,21 +10756,6 @@
       <c r="A33" s="67" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-05</t>
-        </is>
-      </c>
-      <c r="C33" s="67" t="inlineStr">
-        <is>
-          <t>행정문서 수집·정형화 → AI 어시스턴트 행정 지원</t>
-        </is>
-      </c>
-      <c r="D33" s="67" t="inlineStr">
-        <is>
-          <t>시스템관리자</t>
-        </is>
-      </c>
       <c r="E33" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-05-01</t>
@@ -10778,12 +10763,12 @@
       </c>
       <c r="F33" s="67" t="inlineStr">
         <is>
-          <t>첨부문서 업로드</t>
+          <t>AI 대화 세션 관리</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-010-03</t>
+          <t>PR-PAR-010-01</t>
         </is>
       </c>
       <c r="H33" s="67" t="inlineStr">
@@ -10793,23 +10778,23 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>비정형 행정문서 업로드·정형화</t>
+          <t>자연어 질의(sLLM+RAG)</t>
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>- PDF/DOCX 등 비정형 문서 업로드
-- 텍스트 추출·정형화 적재 및 RAG 연계 확인</t>
+          <t>- 자연어 질의 입력
+- sLLM 응답 및 세션 이력 확인</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
         <is>
-          <t>- 비정형 문서가 정형화 적재되고 RAG 검색 대상에 포함</t>
+          <t>- sLLM 자연어 응답이 정상 표출되고 대화 세션·메시지가 관리됨</t>
         </is>
       </c>
       <c r="M33" s="67" t="inlineStr">
@@ -10822,9 +10807,6 @@
       <c r="A34" s="67" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="68" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="68" t="n"/>
       <c r="E34" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-05-02</t>
@@ -10832,12 +10814,12 @@
       </c>
       <c r="F34" s="67" t="inlineStr">
         <is>
-          <t>AI 대화 세션 관리</t>
+          <t>조례 인용·문서 조회</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-010-01</t>
+          <t>PR-PAR-010-02</t>
         </is>
       </c>
       <c r="H34" s="67" t="inlineStr">
@@ -10847,13 +10829,13 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>자연어 질의(sLLM+RAG)</t>
+          <t>RAG 조례 인용 카드</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>- 자연어 질의 입력
-- sLLM 응답 및 세션 이력 확인</t>
+          <t>- 조례 관련 질의
+- 조례명·관련 조문 발췌 응답 확인</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -10863,7 +10845,7 @@
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
-          <t>- sLLM 자연어 응답이 정상 표출되고 대화 세션·메시지가 관리됨</t>
+          <t>- 관련 조례가 조례명·조문 발췌로 표출되고 답변에 반영</t>
         </is>
       </c>
       <c r="M34" s="67" t="inlineStr">
@@ -10873,376 +10855,375 @@
       </c>
     </row>
     <row r="35" ht="78" customHeight="1" s="48">
-      <c r="A35" s="67" t="n">
+      <c r="A35" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="68" t="n"/>
-      <c r="D35" s="68" t="n"/>
-      <c r="E35" s="67" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>TT-PAR-05-03</t>
         </is>
       </c>
-      <c r="F35" s="67" t="inlineStr">
-        <is>
-          <t>조례 인용·문서 조회</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-02</t>
-        </is>
-      </c>
-      <c r="H35" s="67" t="inlineStr">
+      <c r="F35" s="35" t="inlineStr">
+        <is>
+          <t>[화면] AI 어시스턴트(행정조례검색)</t>
+        </is>
+      </c>
+      <c r="G35" s="36" t="inlineStr">
+        <is>
+          <t>PR-PAR-010-01~04</t>
+        </is>
+      </c>
+      <c r="H35" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>RAG 조례 인용 카드</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>- 조례 관련 질의
-- 조례명·관련 조문 발췌 응답 확인</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L35" s="1" t="inlineStr">
-        <is>
-          <t>- 관련 조례가 조례명·조문 발췌로 표출되고 답변에 반영</t>
-        </is>
-      </c>
-      <c r="M35" s="67" t="inlineStr">
-        <is>
-          <t>정정</t>
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>sLLM+RAG 기반 대화형 행정 정보 검색
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J35" s="38" t="inlineStr">
+        <is>
+          <t>- 채팅 영역(조례 인용: 조례명+관련 조문 발췌)
+- sLLM·RAG 정책문서·조례 검색
+- 질문 입력
+- 최근 대화·최근 리포트</t>
+        </is>
+      </c>
+      <c r="K35" s="39" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L35" s="38" t="inlineStr">
+        <is>
+          <t>- AI 어시스턴트(행정조례검색) 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M35" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
     <row r="36" ht="78" customHeight="1" s="48">
-      <c r="A36" s="35" t="n">
+      <c r="A36" s="67" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="68" t="n"/>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="68" t="n"/>
-      <c r="E36" s="35" t="inlineStr">
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-05-04</t>
         </is>
       </c>
-      <c r="F36" s="35" t="inlineStr">
-        <is>
-          <t>[화면] AI 어시스턴트(행정조례검색)</t>
-        </is>
-      </c>
-      <c r="G36" s="36" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-01~04</t>
-        </is>
-      </c>
-      <c r="H36" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="I36" s="37" t="inlineStr">
-        <is>
-          <t>sLLM+RAG 기반 대화형 행정 정보 검색
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J36" s="38" t="inlineStr">
-        <is>
-          <t>- 채팅 영역(조례 인용: 조례명+관련 조문 발췌)
-- sLLM·RAG 정책문서·조례 검색·리포트 생성
-- 질문 입력·파일 첨부(PDF/DOCX)
-- 최근 대화·최근 리포트·자주하는질문</t>
-        </is>
-      </c>
-      <c r="K36" s="39" t="inlineStr">
-        <is>
-          <t>일반사용자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L36" s="38" t="inlineStr">
-        <is>
-          <t>- AI 어시스턴트(행정조례검색) 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M36" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="F36" s="67" t="inlineStr">
+        <is>
+          <t>대량 민원 자동 요약</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-010-01</t>
+        </is>
+      </c>
+      <c r="H36" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-02</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>AI 대량 민원 내용 요약</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>- 대량 민원 대상 자연어 질의
+- AI 응답의 요약 결과 및 [리포트 생성] 확인</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>교통행정과 담당자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t>- 대량 민원 내용이 요약되어 표출되고 리포트 생성 버튼 제공</t>
+        </is>
+      </c>
+      <c r="M36" s="67" t="inlineStr">
+        <is>
+          <t>신규</t>
         </is>
       </c>
     </row>
     <row r="37" ht="78" customHeight="1" s="48">
-      <c r="A37" s="67" t="n">
+      <c r="A37" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="68" t="n"/>
-      <c r="C37" s="68" t="n"/>
-      <c r="D37" s="68" t="n"/>
-      <c r="E37" s="67" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>TT-PAR-05-05</t>
         </is>
       </c>
-      <c r="F37" s="67" t="inlineStr">
-        <is>
-          <t>대량 민원 자동 요약</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-01</t>
-        </is>
-      </c>
-      <c r="H37" s="67" t="inlineStr">
+      <c r="F37" s="35" t="inlineStr">
+        <is>
+          <t>[화면] AI 어시스턴트(대량 민원 자동 요약)</t>
+        </is>
+      </c>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-005-02</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>AI 대량 민원 내용 요약</t>
-        </is>
-      </c>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>- 대량 민원 대상 자연어 질의
-- AI 응답의 요약 결과 및 [리포트 생성] 확인</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr">
-        <is>
-          <t>- 대량 민원 내용이 요약되어 표출되고 리포트 생성 버튼 제공</t>
-        </is>
-      </c>
-      <c r="M37" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="I37" s="37" t="inlineStr">
+        <is>
+          <t>sLLM+RAG 기반 대량 민원 내용 자동 요약
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J37" s="38" t="inlineStr">
+        <is>
+          <t>- 채팅 영역
+- AI 응답 시 대량 민원 내용 요약(리포트 생성 버튼 제공)</t>
+        </is>
+      </c>
+      <c r="K37" s="39" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L37" s="38" t="inlineStr">
+        <is>
+          <t>- AI 어시스턴트(대량 민원 자동 요약) 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M37" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1" s="48">
-      <c r="A38" s="35" t="n">
+      <c r="A38" s="67" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="68" t="n"/>
-      <c r="C38" s="68" t="n"/>
-      <c r="D38" s="68" t="n"/>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E38" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-05-06</t>
         </is>
       </c>
-      <c r="F38" s="35" t="inlineStr">
-        <is>
-          <t>[화면] AI 어시스턴트(대량 민원 자동 요약)</t>
-        </is>
-      </c>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-02</t>
-        </is>
-      </c>
-      <c r="I38" s="37" t="inlineStr">
-        <is>
-          <t>sLLM+RAG 기반 대량 민원 내용 자동 요약
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J38" s="38" t="inlineStr">
-        <is>
-          <t>- 채팅 영역
-- AI 응답 시 대량 민원 내용 요약(리포트 생성 버튼 제공)</t>
-        </is>
-      </c>
-      <c r="K38" s="39" t="inlineStr">
-        <is>
-          <t>일반사용자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L38" s="38" t="inlineStr">
-        <is>
-          <t>- AI 어시스턴트(대량 민원 자동 요약) 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M38" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="F38" s="67" t="inlineStr">
+        <is>
+          <t>요약 보고서 미리보기·다운로드</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-010-01</t>
+        </is>
+      </c>
+      <c r="H38" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-03</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>민원요약 보고서 출력</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>- [리포트 생성] 후 미리보기
+- PDF/DOCX 다운로드</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>교통행정과 담당자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>- 민원요약 보고서 미리보기 표출 및 PDF·DOCX 다운로드</t>
+        </is>
+      </c>
+      <c r="M38" s="67" t="inlineStr">
+        <is>
+          <t>신규</t>
         </is>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1" s="48">
-      <c r="A39" s="67" t="n">
+      <c r="A39" s="35" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="68" t="n"/>
-      <c r="C39" s="68" t="n"/>
-      <c r="D39" s="68" t="n"/>
-      <c r="E39" s="67" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>TT-PAR-05-07</t>
         </is>
       </c>
-      <c r="F39" s="67" t="inlineStr">
-        <is>
-          <t>요약 보고서 미리보기·다운로드</t>
-        </is>
-      </c>
-      <c r="G39" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-01</t>
-        </is>
-      </c>
-      <c r="H39" s="67" t="inlineStr">
+      <c r="F39" s="35" t="inlineStr">
+        <is>
+          <t>[화면] AI 어시스턴트(보고서 미리보기·다운로드)</t>
+        </is>
+      </c>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-005-03</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>민원요약 보고서 출력</t>
-        </is>
-      </c>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>- [리포트 생성] 후 미리보기
-- PDF/DOCX 다운로드</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr">
-        <is>
-          <t>- 민원요약 보고서 미리보기 표출 및 PDF·DOCX 다운로드</t>
-        </is>
-      </c>
-      <c r="M39" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="I39" s="37" t="inlineStr">
+        <is>
+          <t>민원요약 보고서 미리보기·다운로드
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J39" s="38" t="inlineStr">
+        <is>
+          <t>- 민원요약 보고서 미리보기
+- 보고서 다운로드(PDF, DOCX)</t>
+        </is>
+      </c>
+      <c r="K39" s="39" t="inlineStr">
+        <is>
+          <t>일반사용자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L39" s="38" t="inlineStr">
+        <is>
+          <t>- AI 어시스턴트(보고서 미리보기·다운로드) 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M39" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1" s="48">
-      <c r="A40" s="35" t="n">
+      <c r="A40" s="67" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="68" t="n"/>
-      <c r="C40" s="68" t="n"/>
-      <c r="D40" s="68" t="n"/>
-      <c r="E40" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-08</t>
-        </is>
-      </c>
-      <c r="F40" s="35" t="inlineStr">
-        <is>
-          <t>[화면] AI 어시스턴트(보고서 미리보기·다운로드)</t>
-        </is>
-      </c>
-      <c r="G40" s="36" t="n"/>
-      <c r="H40" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-03</t>
-        </is>
-      </c>
-      <c r="I40" s="37" t="inlineStr">
-        <is>
-          <t>민원요약 보고서 미리보기·다운로드
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J40" s="38" t="inlineStr">
-        <is>
-          <t>- 민원요약 보고서 미리보기
-- 보고서 다운로드(PDF, DOCX)</t>
-        </is>
-      </c>
-      <c r="K40" s="39" t="inlineStr">
-        <is>
-          <t>일반사용자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L40" s="38" t="inlineStr">
-        <is>
-          <t>- AI 어시스턴트(보고서 미리보기·다운로드) 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M40" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="B40" s="67" t="inlineStr">
+        <is>
+          <t>ITS-PAR-06</t>
+        </is>
+      </c>
+      <c r="C40" s="67" t="inlineStr">
+        <is>
+          <t>정기 보고서 자동 생성 설정 → 열람</t>
+        </is>
+      </c>
+      <c r="D40" s="67" t="inlineStr">
+        <is>
+          <t>서비스관리자,
+일반사용자</t>
+        </is>
+      </c>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-06-01</t>
+        </is>
+      </c>
+      <c r="F40" s="67" t="inlineStr">
+        <is>
+          <t>보고서 자동생성 설정</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-008-02</t>
+        </is>
+      </c>
+      <c r="H40" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>배포주기·배포일자 설정</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>- 배포 주기/일자 선택 후 [보고서 자동 생성]</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>서비스관리자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t>- 자동 생성 설정 저장 및 자동 생성 목록에 항목 추가</t>
+        </is>
+      </c>
+      <c r="M40" s="67" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1" s="48">
-      <c r="A41" s="67" t="n">
+      <c r="A41" s="35" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="69" t="n"/>
-      <c r="C41" s="69" t="n"/>
-      <c r="D41" s="69" t="n"/>
-      <c r="E41" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-05-09</t>
-        </is>
-      </c>
-      <c r="F41" s="67" t="inlineStr">
-        <is>
-          <t>자주하는질문 관리</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-010-04</t>
-        </is>
-      </c>
-      <c r="H41" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>AI 추천 질의</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>- 자주하는질문 등록/노출 확인</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr">
-        <is>
-          <t>- 자주하는질문이 관리되고 AI 추천 질의로 노출</t>
-        </is>
-      </c>
-      <c r="M41" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="B41" s="68" t="n"/>
+      <c r="C41" s="68" t="n"/>
+      <c r="D41" s="68" t="n"/>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-06-02</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 보고서 관리</t>
+        </is>
+      </c>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>PR-PAR-008-02</t>
+        </is>
+      </c>
+      <c r="H41" s="35" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="I41" s="37" t="inlineStr">
+        <is>
+          <t>민원 분석 결과 보고서 자동 생성 관리(관리자 전용)
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J41" s="38" t="inlineStr">
+        <is>
+          <t>- 자동 생성 설정(배포부서/배포주기/배포일자 드롭다운·자동생성 버튼)
+- 자동 생성 설정 목록(조회·수정·삭제)</t>
+        </is>
+      </c>
+      <c r="K41" s="39" t="inlineStr">
+        <is>
+          <t>서비스관리자 권한 계정</t>
+        </is>
+      </c>
+      <c r="L41" s="38" t="inlineStr">
+        <is>
+          <t>- 보고서 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M41" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
@@ -11250,60 +11231,47 @@
       <c r="A42" s="67" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-06</t>
-        </is>
-      </c>
-      <c r="C42" s="67" t="inlineStr">
-        <is>
-          <t>정기 보고서 자동 생성 설정 → 열람</t>
-        </is>
-      </c>
-      <c r="D42" s="67" t="inlineStr">
-        <is>
-          <t>서비스관리자,
-일반사용자</t>
-        </is>
-      </c>
+      <c r="B42" s="68" t="n"/>
+      <c r="C42" s="68" t="n"/>
+      <c r="D42" s="68" t="n"/>
       <c r="E42" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-06-01</t>
+          <t>TT-PAR-06-03</t>
         </is>
       </c>
       <c r="F42" s="67" t="inlineStr">
         <is>
-          <t>보고서 자동생성 설정</t>
+          <t>보고서 목록 조회·열람</t>
         </is>
       </c>
       <c r="G42" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-008-02</t>
+          <t>PR-PAR-008-01</t>
         </is>
       </c>
       <c r="H42" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>배포주기·배포일자 설정</t>
+          <t>미리보기·다운로드·열람</t>
         </is>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>- 배포 주기/일자 선택 후 [보고서 자동 생성]</t>
+          <t>- [미리보기] 후 [PDF] 다운로드</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>서비스관리자 권한 계정</t>
+          <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
         <is>
-          <t>- 자동 생성 설정 저장 및 자동 생성 목록에 항목 추가</t>
+          <t>- 미리보기 팝업 표출 및 PDF 다운로드</t>
         </is>
       </c>
       <c r="M42" s="67" t="inlineStr">
@@ -11316,49 +11284,49 @@
       <c r="A43" s="35" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="68" t="n"/>
-      <c r="C43" s="68" t="n"/>
-      <c r="D43" s="68" t="n"/>
+      <c r="B43" s="69" t="n"/>
+      <c r="C43" s="69" t="n"/>
+      <c r="D43" s="69" t="n"/>
       <c r="E43" s="35" t="inlineStr">
         <is>
-          <t>TT-PAR-06-02</t>
+          <t>TT-PAR-06-04</t>
         </is>
       </c>
       <c r="F43" s="35" t="inlineStr">
         <is>
-          <t>[화면] 보고서 관리</t>
+          <t>[화면] 보고서 목록</t>
         </is>
       </c>
       <c r="G43" s="36" t="inlineStr">
         <is>
-          <t>PR-PAR-008-02</t>
+          <t>PR-PAR-008-01</t>
         </is>
       </c>
       <c r="H43" s="35" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="I43" s="37" t="inlineStr">
         <is>
-          <t>민원 분석 결과 보고서 자동 생성 관리(관리자 전용)
+          <t>민원 분석 결과 보고서 목록 조회
 (화면설계 점검)</t>
         </is>
       </c>
       <c r="J43" s="38" t="inlineStr">
         <is>
-          <t>- 자동 생성 설정(배포부서/배포주기/배포일자 드롭다운·자동생성 버튼)
-- 자동 생성 설정 목록(조회·수정·삭제)</t>
+          <t>- 자동생성 보고서 목록(보고서명/배포주기/생성자/부서/생성일/상태·미리보기·PDF·DOCX)
+- 직접생성 보고서 목록(내보내기 출처/분석기간/생성자/부서·미리보기·다운로드)</t>
         </is>
       </c>
       <c r="K43" s="39" t="inlineStr">
         <is>
-          <t>서비스관리자 권한 계정</t>
+          <t>일반사용자 권한 계정</t>
         </is>
       </c>
       <c r="L43" s="38" t="inlineStr">
         <is>
-          <t>- 보고서 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- 보고서 목록 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M43" s="35" t="inlineStr">
@@ -11371,47 +11339,61 @@
       <c r="A44" s="67" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="68" t="n"/>
-      <c r="C44" s="68" t="n"/>
-      <c r="D44" s="68" t="n"/>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>ITS-PAR-07</t>
+        </is>
+      </c>
+      <c r="C44" s="67" t="inlineStr">
+        <is>
+          <t>감시 솔루션 데이터 융합(AI 어시스턴트 질의) → 통합분석 → 보고서</t>
+        </is>
+      </c>
+      <c r="D44" s="67" t="inlineStr">
+        <is>
+          <t>서비스관리자,
+일반사용자</t>
+        </is>
+      </c>
       <c r="E44" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-06-03</t>
+          <t>TT-PAR-07-01</t>
         </is>
       </c>
       <c r="F44" s="67" t="inlineStr">
         <is>
-          <t>보고서 목록 조회·열람</t>
+          <t>AI 대화 세션 관리(융합 질의)</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-008-01</t>
+          <t>PR-PAR-010-01</t>
         </is>
       </c>
       <c r="H44" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005-04</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>미리보기·다운로드·열람</t>
+          <t>데이터 융합 질의·통합분석</t>
         </is>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>- [미리보기] 후 [PDF] 다운로드</t>
+          <t>- AI 어시스턴트로 두 솔루션(주차민원+공영주차장 안전) 융합 질의
+- 상관관계·종합 인사이트 도출</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
         <is>
-          <t>- 미리보기 팝업 표출 및 PDF 다운로드</t>
+          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화</t>
         </is>
       </c>
       <c r="M44" s="67" t="inlineStr">
@@ -11424,49 +11406,46 @@
       <c r="A45" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="69" t="n"/>
-      <c r="C45" s="69" t="n"/>
-      <c r="D45" s="69" t="n"/>
+      <c r="B45" s="68" t="n"/>
+      <c r="C45" s="68" t="n"/>
+      <c r="D45" s="68" t="n"/>
       <c r="E45" s="35" t="inlineStr">
         <is>
-          <t>TT-PAR-06-04</t>
+          <t>TT-PAR-07-02</t>
         </is>
       </c>
       <c r="F45" s="35" t="inlineStr">
         <is>
-          <t>[화면] 보고서 목록</t>
-        </is>
-      </c>
-      <c r="G45" s="36" t="inlineStr">
-        <is>
-          <t>PR-PAR-008-01</t>
-        </is>
-      </c>
+          <t>[화면] AI 어시스턴트(통합분석)</t>
+        </is>
+      </c>
+      <c r="G45" s="36" t="n"/>
       <c r="H45" s="35" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005-04</t>
         </is>
       </c>
       <c r="I45" s="37" t="inlineStr">
         <is>
-          <t>민원 분석 결과 보고서 목록 조회
+          <t>민원데이터와 감시(화재·안전) 데이터를 결합한 통합분석
 (화면설계 점검)</t>
         </is>
       </c>
       <c r="J45" s="38" t="inlineStr">
         <is>
-          <t>- 자동생성 보고서 목록(보고서명/배포주기/생성자/부서/생성일/상태·미리보기·PDF·DOCX)
-- 직접생성 보고서 목록(내보내기 출처/분석기간/생성자/부서·미리보기·다운로드)</t>
+          <t>- 채팅 영역
+- 결합이 필요한 질문에 AI 에이전트 호출·융합 데이터에서 종합 인사이트 도출
+- 결과를 AI 어시스턴트 답변으로 표시(리포트 생성 버튼 제공)</t>
         </is>
       </c>
       <c r="K45" s="39" t="inlineStr">
         <is>
-          <t>일반사용자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="L45" s="38" t="inlineStr">
         <is>
-          <t>- 보고서 목록 화면의 설계 기능이 모두 정상 표출·동작</t>
+          <t>- AI 어시스턴트(통합분석) 화면의 설계 기능이 모두 정상 표출·동작</t>
         </is>
       </c>
       <c r="M45" s="35" t="inlineStr">
@@ -11479,51 +11458,37 @@
       <c r="A46" s="67" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-07</t>
-        </is>
-      </c>
-      <c r="C46" s="67" t="inlineStr">
-        <is>
-          <t>감시 솔루션 데이터 융합(AI 어시스턴트 질의) → 통합분석 → 보고서</t>
-        </is>
-      </c>
-      <c r="D46" s="67" t="inlineStr">
-        <is>
-          <t>서비스관리자,
-일반사용자</t>
-        </is>
-      </c>
+      <c r="B46" s="69" t="n"/>
+      <c r="C46" s="69" t="n"/>
+      <c r="D46" s="69" t="n"/>
       <c r="E46" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-07-01</t>
+          <t>TT-PAR-07-03</t>
         </is>
       </c>
       <c r="F46" s="67" t="inlineStr">
         <is>
-          <t>AI 대화 세션 관리(융합 질의)</t>
+          <t>보고서 목록 조회(반영)</t>
         </is>
       </c>
       <c r="G46" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-010-01</t>
+          <t>PR-PAR-008-01</t>
         </is>
       </c>
       <c r="H46" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-005-04</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>데이터 융합 질의·통합분석</t>
+          <t>융합 분석 보고서 반영</t>
         </is>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>- AI 어시스턴트로 두 솔루션(주차민원+공영주차장 안전) 융합 질의
-- 상관관계·종합 인사이트 도출</t>
+          <t>- 융합 분석 결과 보고서 내보내기·확인</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -11533,7 +11498,7 @@
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화</t>
+          <t>- 융합 분석 인사이트가 보고서에 반영·다운로드</t>
         </is>
       </c>
       <c r="M46" s="67" t="inlineStr">
@@ -11543,54 +11508,67 @@
       </c>
     </row>
     <row r="47" ht="78" customHeight="1" s="48">
-      <c r="A47" s="35" t="n">
+      <c r="A47" s="67" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="68" t="n"/>
-      <c r="C47" s="68" t="n"/>
-      <c r="D47" s="68" t="n"/>
-      <c r="E47" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-07-02</t>
-        </is>
-      </c>
-      <c r="F47" s="35" t="inlineStr">
-        <is>
-          <t>[화면] AI 어시스턴트(통합분석)</t>
-        </is>
-      </c>
-      <c r="G47" s="36" t="n"/>
-      <c r="H47" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-04</t>
-        </is>
-      </c>
-      <c r="I47" s="37" t="inlineStr">
-        <is>
-          <t>민원데이터와 감시(화재·안전) 데이터를 결합한 통합분석
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J47" s="38" t="inlineStr">
-        <is>
-          <t>- 채팅 영역
-- 결합이 필요한 질문에 AI 에이전트 호출·융합 데이터에서 종합 인사이트 도출
-- 결과를 AI 어시스턴트 답변으로 표시(리포트 생성 버튼 제공)</t>
-        </is>
-      </c>
-      <c r="K47" s="39" t="inlineStr">
+      <c r="B47" s="67" t="inlineStr">
+        <is>
+          <t>ITS-PAR-08</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="inlineStr">
+        <is>
+          <t>분석지표 가중치·설정 전환 → 기능 재검증</t>
+        </is>
+      </c>
+      <c r="D47" s="67" t="inlineStr">
+        <is>
+          <t>시스템관리자</t>
+        </is>
+      </c>
+      <c r="E47" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-01</t>
+        </is>
+      </c>
+      <c r="F47" s="67" t="inlineStr">
+        <is>
+          <t>분석지표 가중치 조회</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-011-01</t>
+        </is>
+      </c>
+      <c r="H47" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-03</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>분석모델별 지표·가중치 조회</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>- 분석지표 가중치 화면 진입, 분석모델별 지표·가중치 목록 확인</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L47" s="38" t="inlineStr">
-        <is>
-          <t>- AI 어시스턴트(통합분석) 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M47" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>- 분석모델별 지표·가중치가 정상 조회</t>
+        </is>
+      </c>
+      <c r="M47" s="67" t="inlineStr">
+        <is>
+          <t>신규</t>
         </is>
       </c>
     </row>
@@ -11598,37 +11576,37 @@
       <c r="A48" s="67" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="69" t="n"/>
-      <c r="C48" s="69" t="n"/>
-      <c r="D48" s="69" t="n"/>
+      <c r="B48" s="68" t="n"/>
+      <c r="C48" s="68" t="n"/>
+      <c r="D48" s="68" t="n"/>
       <c r="E48" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-07-03</t>
+          <t>TT-PAR-08-02</t>
         </is>
       </c>
       <c r="F48" s="67" t="inlineStr">
         <is>
-          <t>보고서 목록 조회(반영)</t>
+          <t>분석지표 가중치 저장</t>
         </is>
       </c>
       <c r="G48" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-008-01</t>
+          <t>PR-PAR-011-02</t>
         </is>
       </c>
       <c r="H48" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-006-03</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>융합 분석 보고서 반영</t>
+          <t>타 지자체 기준 가중치 변경·저장(확산)</t>
         </is>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>- 융합 분석 결과 보고서 내보내기·확인</t>
+          <t>- 대상 지역 여건에 맞는 지표·가중치로 변경 후 저장</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -11638,12 +11616,12 @@
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
-          <t>- 융합 분석 인사이트가 보고서에 반영·다운로드</t>
+          <t>- 변경 가중치가 저장되고 변경이력이 함께 기록</t>
         </is>
       </c>
       <c r="M48" s="67" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>신규</t>
         </is>
       </c>
     </row>
@@ -11651,34 +11629,22 @@
       <c r="A49" s="67" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="67" t="inlineStr">
-        <is>
-          <t>ITS-PAR-08</t>
-        </is>
-      </c>
-      <c r="C49" s="67" t="inlineStr">
-        <is>
-          <t>분석지표 가중치·설정 전환 → 기능 재검증</t>
-        </is>
-      </c>
-      <c r="D49" s="67" t="inlineStr">
-        <is>
-          <t>시스템관리자</t>
-        </is>
-      </c>
+      <c r="B49" s="68" t="n"/>
+      <c r="C49" s="68" t="n"/>
+      <c r="D49" s="68" t="n"/>
       <c r="E49" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-01</t>
+          <t>TT-PAR-08-03</t>
         </is>
       </c>
       <c r="F49" s="67" t="inlineStr">
         <is>
-          <t>분석지표 가중치 조회</t>
+          <t>가중치 변경이력 조회</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-011-01</t>
+          <t>PR-PAR-011-03</t>
         </is>
       </c>
       <c r="H49" s="67" t="inlineStr">
@@ -11688,12 +11654,12 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>분석모델별 지표·가중치 조회</t>
+          <t>변경이력 조회</t>
         </is>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>- 분석지표 가중치 화면 진입, 분석모델별 지표·가중치 목록 확인</t>
+          <t>- 변경항목·내용·사유·변경자 확인</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -11703,7 +11669,7 @@
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>- 분석모델별 지표·가중치가 정상 조회</t>
+          <t>- 가중치 변경이력이 항목·사유·변경자와 함께 표출</t>
         </is>
       </c>
       <c r="M49" s="67" t="inlineStr">
@@ -11721,17 +11687,17 @@
       <c r="D50" s="68" t="n"/>
       <c r="E50" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-02</t>
+          <t>TT-PAR-08-04</t>
         </is>
       </c>
       <c r="F50" s="67" t="inlineStr">
         <is>
-          <t>분석지표 가중치 저장</t>
+          <t>가중치 설정 롤백</t>
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-011-02</t>
+          <t>PR-PAR-011-04</t>
         </is>
       </c>
       <c r="H50" s="67" t="inlineStr">
@@ -11741,12 +11707,12 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>타 지자체 기준 가중치 변경·저장(확산)</t>
+          <t>이전 설정 롤백</t>
         </is>
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>- 대상 지역 여건에 맞는 지표·가중치로 변경 후 저장</t>
+          <t>- 특정 변경이력 선택 후 롤백</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -11756,7 +11722,7 @@
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
-          <t>- 변경 가중치가 저장되고 변경이력이 함께 기록</t>
+          <t>- 이전 가중치 설정으로 정상 복원</t>
         </is>
       </c>
       <c r="M50" s="67" t="inlineStr">
@@ -11766,55 +11732,59 @@
       </c>
     </row>
     <row r="51" ht="78" customHeight="1" s="48">
-      <c r="A51" s="67" t="n">
+      <c r="A51" s="35" t="n">
         <v>46</v>
       </c>
       <c r="B51" s="68" t="n"/>
       <c r="C51" s="68" t="n"/>
       <c r="D51" s="68" t="n"/>
-      <c r="E51" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-03</t>
-        </is>
-      </c>
-      <c r="F51" s="67" t="inlineStr">
-        <is>
-          <t>가중치 변경이력 조회</t>
-        </is>
-      </c>
-      <c r="G51" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-011-03</t>
-        </is>
-      </c>
-      <c r="H51" s="67" t="inlineStr">
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-05</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 설정_분석지표 가중치설정</t>
+        </is>
+      </c>
+      <c r="G51" s="36" t="inlineStr">
+        <is>
+          <t>PR-PAR-011-01~04</t>
+        </is>
+      </c>
+      <c r="H51" s="35" t="inlineStr">
         <is>
           <t>UI-PAR-006-03</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>변경이력 조회</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>- 변경항목·내용·사유·변경자 확인</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="I51" s="37" t="inlineStr">
+        <is>
+          <t>분석지표 가중치를 지역 여건에 맞게 조정·이력 관리
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J51" s="38" t="inlineStr">
+        <is>
+          <t>- 분석유형별 탭 가중치 조절
+- 가중치 변경 이력 표시
+- 설정 저장(변경 내용 이력 기록)
+- 기본값 초기화(롤백)</t>
+        </is>
+      </c>
+      <c r="K51" s="39" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L51" s="1" t="inlineStr">
-        <is>
-          <t>- 가중치 변경이력이 항목·사유·변경자와 함께 표출</t>
-        </is>
-      </c>
-      <c r="M51" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="L51" s="38" t="inlineStr">
+        <is>
+          <t>- 설정_분석지표 가중치설정 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M51" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
@@ -11827,32 +11797,32 @@
       <c r="D52" s="68" t="n"/>
       <c r="E52" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-04</t>
+          <t>TT-PAR-08-06</t>
         </is>
       </c>
       <c r="F52" s="67" t="inlineStr">
         <is>
-          <t>가중치 설정 롤백</t>
+          <t>메뉴별 권한 조회</t>
         </is>
       </c>
       <c r="G52" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-011-04</t>
+          <t>PR-CMM-003-01</t>
         </is>
       </c>
       <c r="H52" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-006-03</t>
+          <t>UI-PAR-006-02</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>이전 설정 롤백</t>
+          <t>권한별 메뉴 권한 조회</t>
         </is>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>- 특정 변경이력 선택 후 롤백</t>
+          <t>- 좌측 기등록 메뉴목록·우측 권한별 체크 상태 확인</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -11862,7 +11832,7 @@
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
-          <t>- 이전 가중치 설정으로 정상 복원</t>
+          <t>- 권한별 메뉴 권한 부여 현황이 정상 조회</t>
         </is>
       </c>
       <c r="M52" s="67" t="inlineStr">
@@ -11872,112 +11842,111 @@
       </c>
     </row>
     <row r="53" ht="78" customHeight="1" s="48">
-      <c r="A53" s="35" t="n">
+      <c r="A53" s="67" t="n">
         <v>48</v>
       </c>
       <c r="B53" s="68" t="n"/>
       <c r="C53" s="68" t="n"/>
       <c r="D53" s="68" t="n"/>
-      <c r="E53" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-05</t>
-        </is>
-      </c>
-      <c r="F53" s="35" t="inlineStr">
-        <is>
-          <t>[화면] 설정_분석지표 가중치설정</t>
-        </is>
-      </c>
-      <c r="G53" s="36" t="inlineStr">
-        <is>
-          <t>PR-PAR-011-01~04</t>
-        </is>
-      </c>
-      <c r="H53" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-03</t>
-        </is>
-      </c>
-      <c r="I53" s="37" t="inlineStr">
-        <is>
-          <t>분석지표 가중치를 지역 여건에 맞게 조정·이력 관리
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J53" s="38" t="inlineStr">
-        <is>
-          <t>- 분석유형별 탭 가중치 조절
-- 가중치 변경 이력 표시
-- 설정 저장(변경 내용 이력 기록)
-- 기본값 초기화(롤백)</t>
-        </is>
-      </c>
-      <c r="K53" s="39" t="inlineStr">
+      <c r="E53" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-07</t>
+        </is>
+      </c>
+      <c r="F53" s="67" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 설정</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>PR-CMM-003-02</t>
+        </is>
+      </c>
+      <c r="H53" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>권한 부여·회수</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>- 기등록 메뉴에 권한 체크(INSERT)/해제(DELETE) 후 저장</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L53" s="38" t="inlineStr">
-        <is>
-          <t>- 설정_분석지표 가중치설정 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M53" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>- 체크=부여, 해제=회수가 반영되고 재로그인 시 메뉴 구성에 적용</t>
+        </is>
+      </c>
+      <c r="M53" s="67" t="inlineStr">
+        <is>
+          <t>신규</t>
         </is>
       </c>
     </row>
     <row r="54" ht="78" customHeight="1" s="48">
-      <c r="A54" s="67" t="n">
+      <c r="A54" s="35" t="n">
         <v>49</v>
       </c>
       <c r="B54" s="68" t="n"/>
       <c r="C54" s="68" t="n"/>
       <c r="D54" s="68" t="n"/>
-      <c r="E54" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-06</t>
-        </is>
-      </c>
-      <c r="F54" s="67" t="inlineStr">
-        <is>
-          <t>공통코드 관리</t>
-        </is>
-      </c>
-      <c r="G54" s="22" t="inlineStr">
-        <is>
-          <t>PR-CMM-002-01</t>
-        </is>
-      </c>
-      <c r="H54" s="67" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>지역·유형 코드 설정</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>- 대상 지역·민원 유형 등 공통코드 등록/수정</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-08</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 설정_메뉴 권한관리</t>
+        </is>
+      </c>
+      <c r="G54" s="36" t="inlineStr">
+        <is>
+          <t>PR-CMM-003-01~02</t>
+        </is>
+      </c>
+      <c r="H54" s="35" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="I54" s="37" t="inlineStr">
+        <is>
+          <t>메뉴별 사용 권한그룹 지정
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J54" s="38" t="inlineStr">
+        <is>
+          <t>- 메뉴별 사용 가능 권한그룹 지정 탭
+- 메뉴 클릭→오른쪽에서 권한그룹 지정(체크 부여/해제)
+- 시스템·서비스관리자 전체권한 고정, 일반사용자 체크 부여·권한 저장</t>
+        </is>
+      </c>
+      <c r="K54" s="39" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L54" s="1" t="inlineStr">
-        <is>
-          <t>- 공통코드가 저장되고 분석·화면 전반에 반영</t>
-        </is>
-      </c>
-      <c r="M54" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="L54" s="38" t="inlineStr">
+        <is>
+          <t>- 설정_메뉴 권한관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M54" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11959,34 @@
       <c r="D55" s="68" t="n"/>
       <c r="E55" s="67" t="inlineStr">
         <is>
-          <t>TT-PAR-08-07</t>
+          <t>TT-PAR-08-09</t>
         </is>
       </c>
       <c r="F55" s="67" t="inlineStr">
         <is>
-          <t>메뉴별 권한 조회</t>
+          <t>메뉴 권한 관리 조회</t>
         </is>
       </c>
       <c r="G55" s="22" t="inlineStr">
         <is>
-          <t>PR-CMM-003-01</t>
+          <t>미정의(메뉴 권한 관리)</t>
         </is>
       </c>
       <c r="H55" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-006-02</t>
+          <t>UI-PAR-006-01</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>권한별 메뉴 권한 조회</t>
+          <t>사용자 계정·권한그룹 현황 조회</t>
         </is>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>- 좌측 기등록 메뉴목록·우측 권한별 체크 상태 확인</t>
+          <t>- 설정&gt;메뉴 권한 관리 탭 진입
+- 메뉴 선택 후 권한 그룹 지정 상태 확인
+- 메뉴 단위 저장</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -12025,7 +11996,7 @@
       </c>
       <c r="L55" s="1" t="inlineStr">
         <is>
-          <t>- 권한별 메뉴 권한 부여 현황이 정상 조회</t>
+          <t>- 사용자 계정 현황이 권한그룹별로 조회되고 검색·필터 정상 동작</t>
         </is>
       </c>
       <c r="M55" s="67" t="inlineStr">
@@ -12035,111 +12006,108 @@
       </c>
     </row>
     <row r="56" ht="78" customHeight="1" s="48">
-      <c r="A56" s="67" t="n">
+      <c r="A56" s="35" t="n">
         <v>51</v>
       </c>
       <c r="B56" s="68" t="n"/>
       <c r="C56" s="68" t="n"/>
       <c r="D56" s="68" t="n"/>
-      <c r="E56" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-08</t>
-        </is>
-      </c>
-      <c r="F56" s="67" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 설정</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="inlineStr">
-        <is>
-          <t>PR-CMM-003-02</t>
-        </is>
-      </c>
-      <c r="H56" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>권한 부여·회수</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>- 기등록 메뉴에 권한 체크(INSERT)/해제(DELETE) 후 저장</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-10</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>[화면] 설정_메뉴 권한 관리</t>
+        </is>
+      </c>
+      <c r="G56" s="36" t="n"/>
+      <c r="H56" s="35" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-01</t>
+        </is>
+      </c>
+      <c r="I56" s="37" t="inlineStr">
+        <is>
+          <t>사용자 계정 현황 조회·권한그룹별 관리
+(화면설계 점검)</t>
+        </is>
+      </c>
+      <c r="J56" s="38" t="inlineStr">
+        <is>
+          <t>- 메뉴 권한 관리/분석 지표 가중치 설정 2개 탭
+- 메뉴별 권한 그룹 지정(시스템 관리자 항상 허용, 일반 사용자 관리 메뉴 부여 불가)
+- 서비스 관리자 해제 시 일반 사용자 동시 해제
+- 메뉴 단위 저장</t>
+        </is>
+      </c>
+      <c r="K56" s="39" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L56" s="1" t="inlineStr">
-        <is>
-          <t>- 체크=부여, 해제=회수가 반영되고 재로그인 시 메뉴 구성에 적용</t>
-        </is>
-      </c>
-      <c r="M56" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
+      <c r="L56" s="38" t="inlineStr">
+        <is>
+          <t>- 설정_메뉴 권한 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
+        </is>
+      </c>
+      <c r="M56" s="35" t="inlineStr">
+        <is>
+          <t>화면설계</t>
         </is>
       </c>
     </row>
     <row r="57" ht="78" customHeight="1" s="48">
-      <c r="A57" s="35" t="n">
+      <c r="A57" s="67" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="68" t="n"/>
-      <c r="C57" s="68" t="n"/>
-      <c r="D57" s="68" t="n"/>
-      <c r="E57" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-09</t>
-        </is>
-      </c>
-      <c r="F57" s="35" t="inlineStr">
-        <is>
-          <t>[화면] 설정_메뉴 권한관리</t>
-        </is>
-      </c>
-      <c r="G57" s="36" t="inlineStr">
-        <is>
-          <t>PR-CMM-003-01~02</t>
-        </is>
-      </c>
-      <c r="H57" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="I57" s="37" t="inlineStr">
-        <is>
-          <t>메뉴별 사용 권한그룹 지정
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J57" s="38" t="inlineStr">
-        <is>
-          <t>- 메뉴별 사용 가능 권한그룹 지정 탭
-- 메뉴 클릭→오른쪽에서 권한그룹 지정(체크 부여/해제)
-- 시스템·서비스관리자 전체권한 고정, 일반사용자 체크 부여·권한 저장</t>
-        </is>
-      </c>
-      <c r="K57" s="39" t="inlineStr">
+      <c r="B57" s="69" t="n"/>
+      <c r="C57" s="69" t="n"/>
+      <c r="D57" s="69" t="n"/>
+      <c r="E57" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-08-11</t>
+        </is>
+      </c>
+      <c r="F57" s="67" t="inlineStr">
+        <is>
+          <t>설정 전환 후 기능 재검증</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-003-01 외 주요 분석</t>
+        </is>
+      </c>
+      <c r="H57" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-003</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>설정 전환 후 주요 분석 재실행</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>- 변경된 지역·가중치·권한 기준으로 집중구역/시뮬레이션/투자우선순위 재실행</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>시스템관리자 권한 계정</t>
         </is>
       </c>
-      <c r="L57" s="38" t="inlineStr">
-        <is>
-          <t>- 설정_메뉴 권한관리 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M57" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>- 변경 설정 기준으로 주요 분석 기능이 오류 없이 정상 동작</t>
+        </is>
+      </c>
+      <c r="M57" s="67" t="inlineStr">
+        <is>
+          <t>정정</t>
         </is>
       </c>
     </row>
@@ -12147,269 +12115,111 @@
       <c r="A58" s="67" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="68" t="n"/>
-      <c r="C58" s="68" t="n"/>
-      <c r="D58" s="68" t="n"/>
-      <c r="E58" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-10</t>
-        </is>
-      </c>
-      <c r="F58" s="67" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리 조회</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="inlineStr">
-        <is>
-          <t>미정의(메뉴 권한 관리)</t>
-        </is>
-      </c>
-      <c r="H58" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>사용자 계정·권한그룹 현황 조회</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>- 설정&gt;메뉴 권한 관리 탭 진입
-- 메뉴 선택 후 권한 그룹 지정 상태 확인
-- 메뉴 단위 저장</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr">
-        <is>
-          <t>- 사용자 계정 현황이 권한그룹별로 조회되고 검색·필터 정상 동작</t>
-        </is>
-      </c>
-      <c r="M58" s="67" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="78" customHeight="1" s="48">
-      <c r="A59" s="35" t="n">
-        <v>54</v>
-      </c>
-      <c r="B59" s="68" t="n"/>
-      <c r="C59" s="68" t="n"/>
-      <c r="D59" s="68" t="n"/>
-      <c r="E59" s="35" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-11</t>
-        </is>
-      </c>
-      <c r="F59" s="35" t="inlineStr">
-        <is>
-          <t>[화면] 설정_메뉴 권한 관리</t>
-        </is>
-      </c>
-      <c r="G59" s="36" t="n"/>
-      <c r="H59" s="35" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="I59" s="37" t="inlineStr">
-        <is>
-          <t>사용자 계정 현황 조회·권한그룹별 관리
-(화면설계 점검)</t>
-        </is>
-      </c>
-      <c r="J59" s="38" t="inlineStr">
-        <is>
-          <t>- 메뉴 권한 관리/분석 지표 가중치 설정 2개 탭
-- 메뉴별 권한 그룹 지정(시스템 관리자 항상 허용, 일반 사용자 관리 메뉴 부여 불가)
-- 서비스 관리자 해제 시 일반 사용자 동시 해제
-- 메뉴 단위 저장</t>
-        </is>
-      </c>
-      <c r="K59" s="39" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L59" s="38" t="inlineStr">
-        <is>
-          <t>- 설정_메뉴 권한 관리 화면의 설계 기능이 모두 정상 표출·동작</t>
-        </is>
-      </c>
-      <c r="M59" s="35" t="inlineStr">
-        <is>
-          <t>화면설계</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="78" customHeight="1" s="48">
-      <c r="A60" s="67" t="n">
-        <v>55</v>
-      </c>
-      <c r="B60" s="69" t="n"/>
-      <c r="C60" s="69" t="n"/>
-      <c r="D60" s="69" t="n"/>
-      <c r="E60" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-08-12</t>
-        </is>
-      </c>
-      <c r="F60" s="67" t="inlineStr">
-        <is>
-          <t>설정 전환 후 기능 재검증</t>
-        </is>
-      </c>
-      <c r="G60" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-003-01 외 주요 분석</t>
-        </is>
-      </c>
-      <c r="H60" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-003</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>설정 전환 후 주요 분석 재실행</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>- 변경된 지역·가중치·권한 기준으로 집중구역/시뮬레이션/투자우선순위 재실행</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr">
-        <is>
-          <t>- 변경 설정 기준으로 주요 분석 기능이 오류 없이 정상 동작</t>
-        </is>
-      </c>
-      <c r="M60" s="67" t="inlineStr">
-        <is>
-          <t>정정</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="78" customHeight="1" s="48">
-      <c r="A61" s="67" t="n">
-        <v>56</v>
-      </c>
-      <c r="B61" s="67" t="inlineStr">
+      <c r="B58" s="67" t="inlineStr">
         <is>
           <t>ITS-PAR-09</t>
         </is>
       </c>
-      <c r="C61" s="67" t="inlineStr">
+      <c r="C58" s="67" t="inlineStr">
         <is>
           <t>예외·비정상 흐름 검증(권한)</t>
         </is>
       </c>
-      <c r="D61" s="67" t="inlineStr">
+      <c r="D58" s="67" t="inlineStr">
         <is>
           <t>시스템관리자,
 서비스관리자,
 일반사용자</t>
         </is>
       </c>
-      <c r="E61" s="67" t="inlineStr">
+      <c r="E58" s="67" t="inlineStr">
         <is>
           <t>TT-PAR-09-01</t>
         </is>
       </c>
-      <c r="F61" s="67" t="inlineStr">
+      <c r="F58" s="67" t="inlineStr">
         <is>
           <t>권한 범위 초과 접근 차단</t>
         </is>
       </c>
-      <c r="G61" s="22" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
         <is>
           <t>PR-CMM-003-03</t>
         </is>
       </c>
-      <c r="H61" s="67" t="inlineStr">
+      <c r="H58" s="67" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>비인가 접근 차단</t>
         </is>
       </c>
-      <c r="J61" s="1" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>- 비인가·타 부서 권한 계정으로 관리 기능/데이터 접근 시도</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>일반사용자 권한 계정</t>
         </is>
       </c>
-      <c r="L61" s="1" t="inlineStr">
+      <c r="L58" s="1" t="inlineStr">
         <is>
           <t>- 권한 범위 초과 접근이 차단되고 안내 메시지 표출</t>
         </is>
       </c>
-      <c r="M61" s="67" t="inlineStr">
+      <c r="M58" s="67" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
     </row>
+    <row r="59" ht="78" customHeight="1" s="48"/>
+    <row r="60" ht="78" customHeight="1" s="48"/>
+    <row r="61" ht="78" customHeight="1" s="48"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B49:B60"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C42:C45"/>
     <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="C47:C57"/>
     <mergeCell ref="D30:D32"/>
-    <mergeCell ref="C49:C60"/>
     <mergeCell ref="D25:D29"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D47:D57"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D44:D46"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="D33:D39"/>
     <mergeCell ref="B6:B16"/>
-    <mergeCell ref="D33:D41"/>
-    <mergeCell ref="D49:D60"/>
+    <mergeCell ref="C40:C43"/>
     <mergeCell ref="B17:B24"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="D17:D24"/>
-    <mergeCell ref="B33:B41"/>
+    <mergeCell ref="B40:B43"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="C33:C39"/>
+    <mergeCell ref="C44:C46"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C33:C41"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="C17:C24"/>
+    <mergeCell ref="B47:B57"/>
+    <mergeCell ref="B44:B46"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="C25:C29"/>
-    <mergeCell ref="D42:D45"/>
     <mergeCell ref="C6:C16"/>
     <mergeCell ref="D6:D16"/>
-    <mergeCell ref="C46:C48"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12422,7 +12232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="6" customWidth="1" style="48" min="1" max="1"/>
@@ -12515,7 +12325,7 @@
     </row>
     <row r="5" ht="60" customHeight="1" s="48">
       <c r="A5" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
@@ -12524,17 +12334,17 @@
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>AI RPA·OCR 기반 비정형 문서 자동 수집·정형화 배치에 대응하는 화면이 화면설계서(JJ_PD_IP_D04)에 없어 화면 ID를 공란 처리함</t>
+          <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" s="40" t="inlineStr">
         <is>
-          <t>배치 모니터링 화면 신설 여부 검토 후 화면설계서 반영</t>
+          <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -12550,31 +12360,31 @@
     </row>
     <row r="6" ht="60" customHeight="1" s="48">
       <c r="A6" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>설계 미반영</t>
+          <t>테스트 환경</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
+          <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
         </is>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E6" s="40" t="inlineStr">
         <is>
-          <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
+          <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>검토중</t>
+          <t>대기</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
@@ -12585,16 +12395,16 @@
     </row>
     <row r="7" ht="60" customHeight="1" s="48">
       <c r="A7" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>테스트 환경</t>
+          <t>미수행</t>
         </is>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
-          <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
+          <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
         </is>
       </c>
       <c r="D7" s="29" t="inlineStr">
@@ -12604,7 +12414,7 @@
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
+          <t>통합테스트 수행 후 결과 기입</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
@@ -12618,41 +12428,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="48">
-      <c r="A8" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>미수행</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="E8" s="40" t="inlineStr">
-        <is>
-          <t>통합테스트 수행 후 결과 기입</t>
-        </is>
-      </c>
-      <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-    </row>
+    <row r="8" ht="60" customHeight="1" s="48"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
